--- a/data/trans_orig/IP31KM06_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM06_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38991</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29828</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48157</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32105</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24310</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40202</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34119</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57167</t>
+          <t>40962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>72168</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89971</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82218</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73052</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>91381</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>69604</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61507</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77399</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>68,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91520</t>
+          <t>67172</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78009</t>
+          <t>59387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101057</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>161124</t>
+          <t>149390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146915</t>
+          <t>137620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174599</t>
+          <t>160555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40841</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32417</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48538</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29306</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22365</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37358</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31,38%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33204</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71334</t>
+          <t>70810</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>60174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>81718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49039</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41342</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57463</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>64086</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56034</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71027</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>65441</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60504</t>
+          <t>72421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>115767</t>
+          <t>114480</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104465</t>
+          <t>103572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126388</t>
+          <t>125116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20518</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14562</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26954</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20205</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29550</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>36070</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26896</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44430</t>
+          <t>45328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35326</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28890</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41282</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>35391</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29884</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70,66%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40670</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>41870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>76060</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67992</t>
+          <t>62526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85526</t>
+          <t>80099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74849</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61482</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>89654</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>84562</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>61711</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>132067</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>39,23%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80623</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65287</t>
+          <t>50980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94332</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>165186</t>
+          <t>136051</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138897</t>
+          <t>119176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217596</t>
+          <t>154120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122464</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>107659</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>135831</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>130975</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83470</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153826</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>60,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>132035</t>
+          <t>115437</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118326</t>
+          <t>103014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147371</t>
+          <t>125660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>263010</t>
+          <t>237902</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210600</t>
+          <t>219833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289299</t>
+          <t>254777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46017</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36829</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55931</t>
+          <t>76954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49899</t>
+          <t>37683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84797</t>
+          <t>55291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>109683</t>
+          <t>104870</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92994</t>
+          <t>90169</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>124180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>86677</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68632</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>98503</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>59,54%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>69492</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>59578</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>78680</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>60,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>51,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95795</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74664</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109562</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>165287</t>
+          <t>156182</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141900</t>
+          <t>136872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181976</t>
+          <t>170883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24651</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17242</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>32014</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>26,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>48,61%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>21013</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>14290</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>27405</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33585</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56871</t>
+          <t>58576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>41212</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33849</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>48621</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>51,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>73,82%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>47882</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>41490</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>54605</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>69,5%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>60,22%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>79,26%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>39194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49971</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>90978</t>
+          <t>88809</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>77644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102028</t>
+          <t>97887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>258759</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>234735</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>286006</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,33%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>227702</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>203170</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>297728</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,49%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>277571</t>
+          <t>208622</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252558</t>
+          <t>188970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>309597</t>
+          <t>230310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>505273</t>
+          <t>467381</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>465170</t>
+          <t>437239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>567817</t>
+          <t>499894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>416936</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>389689</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>440960</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>61,7%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>57,67%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>615</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>417429</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>347403</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>441961</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>64,7%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>68,51%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>454797</t>
+          <t>401610</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>422771</t>
+          <t>379922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>479810</t>
+          <t>421262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>872226</t>
+          <t>818546</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>809682</t>
+          <t>786033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>912329</t>
+          <t>848688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
